--- a/product-definitions/spreadsheet/pm-concentration.xlsx
+++ b/product-definitions/spreadsheet/pm-concentration.xlsx
@@ -285,14 +285,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -341,15 +347,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
@@ -357,22 +360,25 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1720,7 +1726,7 @@
     <col customWidth="1" min="14" max="26" width="17.29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.0" customHeight="1">
+    <row r="1">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,7 +1766,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
     </row>
-    <row r="2" ht="12.0" customHeight="1">
+    <row r="2">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1790,7 +1796,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" ht="12.0" customHeight="1">
+    <row r="3">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -1822,7 +1828,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
     </row>
-    <row r="4" ht="12.0" customHeight="1">
+    <row r="4">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>12</v>
@@ -1854,7 +1860,7 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" ht="12.0" customHeight="1">
+    <row r="5">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>2</v>
@@ -1886,7 +1892,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" ht="12.0" customHeight="1">
+    <row r="6">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>15</v>
@@ -1918,7 +1924,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" ht="12.0" customHeight="1">
+    <row r="7">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>16</v>
@@ -1950,7 +1956,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" ht="12.0" customHeight="1">
+    <row r="8">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>18</v>
@@ -1982,7 +1988,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" ht="12.0" customHeight="1">
+    <row r="9">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>19</v>
@@ -2014,7 +2020,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" ht="12.0" customHeight="1">
+    <row r="10">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>21</v>
@@ -2046,7 +2052,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" ht="12.0" customHeight="1">
+    <row r="11">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>22</v>
@@ -2078,7 +2084,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" ht="12.0" customHeight="1">
+    <row r="12">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>24</v>
@@ -2110,7 +2116,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" ht="12.0" customHeight="1">
+    <row r="13">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -2138,7 +2144,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" ht="12.0" customHeight="1">
+    <row r="14">
       <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
@@ -2168,7 +2174,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" ht="12.0" customHeight="1">
+    <row r="15">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
         <v>10</v>
@@ -2200,7 +2206,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" ht="12.0" customHeight="1">
+    <row r="16">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>12</v>
@@ -2232,7 +2238,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" ht="12.0" customHeight="1">
+    <row r="17">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>2</v>
@@ -2264,7 +2270,7 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" ht="12.0" customHeight="1">
+    <row r="18">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
         <v>15</v>
@@ -2296,7 +2302,7 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" ht="12.0" customHeight="1">
+    <row r="19">
       <c r="A19" s="6"/>
       <c r="B19" s="6" t="s">
         <v>16</v>
@@ -2328,7 +2334,7 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" ht="12.0" customHeight="1">
+    <row r="20">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>18</v>
@@ -2360,7 +2366,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" ht="12.0" customHeight="1">
+    <row r="21">
       <c r="A21" s="6"/>
       <c r="B21" s="6" t="s">
         <v>19</v>
@@ -2392,7 +2398,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" ht="12.0" customHeight="1">
+    <row r="22">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
         <v>21</v>
@@ -2424,7 +2430,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" ht="12.0" customHeight="1">
+    <row r="23">
       <c r="A23" s="6"/>
       <c r="B23" s="7" t="s">
         <v>22</v>
@@ -2456,7 +2462,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" ht="12.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
         <v>24</v>
@@ -2488,7 +2494,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" ht="12.0" customHeight="1">
+    <row r="25">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2516,7 +2522,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" ht="12.0" customHeight="1">
+    <row r="26">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -2546,7 +2552,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" ht="12.0" customHeight="1">
+    <row r="27">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
         <v>10</v>
@@ -2578,7 +2584,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" ht="12.0" customHeight="1">
+    <row r="28">
       <c r="A28" s="6"/>
       <c r="B28" s="6" t="s">
         <v>12</v>
@@ -2610,7 +2616,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" ht="12.0" customHeight="1">
+    <row r="29">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
         <v>2</v>
@@ -2642,7 +2648,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" ht="12.0" customHeight="1">
+    <row r="30">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
         <v>15</v>
@@ -2674,7 +2680,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" ht="12.0" customHeight="1">
+    <row r="31">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
         <v>16</v>
@@ -2706,7 +2712,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" ht="12.0" customHeight="1">
+    <row r="32">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
         <v>18</v>
@@ -2738,7 +2744,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" ht="12.0" customHeight="1">
+    <row r="33">
       <c r="A33" s="6"/>
       <c r="B33" s="6" t="s">
         <v>19</v>
@@ -2770,7 +2776,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" ht="12.0" customHeight="1">
+    <row r="34">
       <c r="A34" s="6"/>
       <c r="B34" s="6" t="s">
         <v>21</v>
@@ -2802,7 +2808,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35" ht="12.0" customHeight="1">
+    <row r="35">
       <c r="A35" s="6"/>
       <c r="B35" s="7" t="s">
         <v>22</v>
@@ -2834,7 +2840,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" ht="12.0" customHeight="1">
+    <row r="36">
       <c r="A36" s="6"/>
       <c r="B36" s="6" t="s">
         <v>24</v>
@@ -2866,7 +2872,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" ht="12.0" customHeight="1">
+    <row r="37">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
@@ -2894,7 +2900,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" ht="12.0" customHeight="1">
+    <row r="38">
       <c r="A38" s="5" t="s">
         <v>30</v>
       </c>
@@ -2924,7 +2930,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" ht="12.0" customHeight="1">
+    <row r="39">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
         <v>10</v>
@@ -2956,7 +2962,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" ht="12.0" customHeight="1">
+    <row r="40">
       <c r="A40" s="6"/>
       <c r="B40" s="6" t="s">
         <v>12</v>
@@ -2988,7 +2994,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" ht="12.0" customHeight="1">
+    <row r="41">
       <c r="A41" s="6"/>
       <c r="B41" s="6" t="s">
         <v>2</v>
@@ -3020,7 +3026,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" ht="12.0" customHeight="1">
+    <row r="42">
       <c r="A42" s="6"/>
       <c r="B42" s="6" t="s">
         <v>15</v>
@@ -3052,7 +3058,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" ht="12.0" customHeight="1">
+    <row r="43">
       <c r="A43" s="6"/>
       <c r="B43" s="6" t="s">
         <v>16</v>
@@ -3084,7 +3090,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" ht="12.0" customHeight="1">
+    <row r="44">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
         <v>18</v>
@@ -3116,7 +3122,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" ht="12.0" customHeight="1">
+    <row r="45">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
         <v>19</v>
@@ -3148,7 +3154,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" ht="12.0" customHeight="1">
+    <row r="46">
       <c r="A46" s="6"/>
       <c r="B46" s="6" t="s">
         <v>21</v>
@@ -3180,7 +3186,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" ht="12.0" customHeight="1">
+    <row r="47">
       <c r="A47" s="6"/>
       <c r="B47" s="7" t="s">
         <v>22</v>
@@ -3212,7 +3218,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" ht="12.0" customHeight="1">
+    <row r="48">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
         <v>24</v>
@@ -3244,7 +3250,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" ht="12.0" customHeight="1">
+    <row r="49">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3272,7 +3278,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" ht="12.0" customHeight="1">
+    <row r="50">
       <c r="A50" s="5" t="s">
         <v>32</v>
       </c>
@@ -3302,7 +3308,7 @@
       <c r="Y50" s="6"/>
       <c r="Z50" s="6"/>
     </row>
-    <row r="51" ht="12.0" customHeight="1">
+    <row r="51">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
         <v>10</v>
@@ -3334,7 +3340,7 @@
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
     </row>
-    <row r="52" ht="12.0" customHeight="1">
+    <row r="52">
       <c r="A52" s="6"/>
       <c r="B52" s="6" t="s">
         <v>12</v>
@@ -3366,7 +3372,7 @@
       <c r="Y52" s="6"/>
       <c r="Z52" s="6"/>
     </row>
-    <row r="53" ht="12.0" customHeight="1">
+    <row r="53">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
         <v>2</v>
@@ -3398,7 +3404,7 @@
       <c r="Y53" s="6"/>
       <c r="Z53" s="6"/>
     </row>
-    <row r="54" ht="12.0" customHeight="1">
+    <row r="54">
       <c r="A54" s="6"/>
       <c r="B54" s="6" t="s">
         <v>15</v>
@@ -3430,7 +3436,7 @@
       <c r="Y54" s="6"/>
       <c r="Z54" s="6"/>
     </row>
-    <row r="55" ht="12.0" customHeight="1">
+    <row r="55">
       <c r="A55" s="6"/>
       <c r="B55" s="6" t="s">
         <v>16</v>
@@ -3462,7 +3468,7 @@
       <c r="Y55" s="6"/>
       <c r="Z55" s="6"/>
     </row>
-    <row r="56" ht="12.0" customHeight="1">
+    <row r="56">
       <c r="A56" s="6"/>
       <c r="B56" s="6" t="s">
         <v>18</v>
@@ -3494,7 +3500,7 @@
       <c r="Y56" s="6"/>
       <c r="Z56" s="6"/>
     </row>
-    <row r="57" ht="12.0" customHeight="1">
+    <row r="57">
       <c r="A57" s="6"/>
       <c r="B57" s="6" t="s">
         <v>19</v>
@@ -3526,7 +3532,7 @@
       <c r="Y57" s="6"/>
       <c r="Z57" s="6"/>
     </row>
-    <row r="58" ht="12.0" customHeight="1">
+    <row r="58">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>21</v>
@@ -3558,7 +3564,7 @@
       <c r="Y58" s="6"/>
       <c r="Z58" s="6"/>
     </row>
-    <row r="59" ht="12.0" customHeight="1">
+    <row r="59">
       <c r="A59" s="6"/>
       <c r="B59" s="7" t="s">
         <v>22</v>
@@ -3590,7 +3596,7 @@
       <c r="Y59" s="6"/>
       <c r="Z59" s="6"/>
     </row>
-    <row r="60" ht="12.0" customHeight="1">
+    <row r="60">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
         <v>24</v>
@@ -3622,7 +3628,7 @@
       <c r="Y60" s="6"/>
       <c r="Z60" s="6"/>
     </row>
-    <row r="61" ht="12.0" customHeight="1">
+    <row r="61">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -3650,7 +3656,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" ht="12.0" customHeight="1">
+    <row r="62">
       <c r="A62" s="10" t="s">
         <v>34</v>
       </c>
@@ -3680,7 +3686,7 @@
       <c r="Y62" s="6"/>
       <c r="Z62" s="6"/>
     </row>
-    <row r="63" ht="12.0" customHeight="1">
+    <row r="63">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
         <v>10</v>
@@ -3712,7 +3718,7 @@
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
     </row>
-    <row r="64" ht="12.0" customHeight="1">
+    <row r="64">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
         <v>12</v>
@@ -3744,7 +3750,7 @@
       <c r="Y64" s="6"/>
       <c r="Z64" s="6"/>
     </row>
-    <row r="65" ht="12.0" customHeight="1">
+    <row r="65">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
         <v>2</v>
@@ -3776,7 +3782,7 @@
       <c r="Y65" s="6"/>
       <c r="Z65" s="6"/>
     </row>
-    <row r="66" ht="12.0" customHeight="1">
+    <row r="66">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
         <v>15</v>
@@ -3808,7 +3814,7 @@
       <c r="Y66" s="6"/>
       <c r="Z66" s="6"/>
     </row>
-    <row r="67" ht="12.0" customHeight="1">
+    <row r="67">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
         <v>16</v>
@@ -3840,7 +3846,7 @@
       <c r="Y67" s="6"/>
       <c r="Z67" s="6"/>
     </row>
-    <row r="68" ht="12.0" customHeight="1">
+    <row r="68">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
         <v>18</v>
@@ -3872,7 +3878,7 @@
       <c r="Y68" s="6"/>
       <c r="Z68" s="6"/>
     </row>
-    <row r="69" ht="12.0" customHeight="1">
+    <row r="69">
       <c r="A69" s="6"/>
       <c r="B69" s="6" t="s">
         <v>19</v>
@@ -3904,7 +3910,7 @@
       <c r="Y69" s="6"/>
       <c r="Z69" s="6"/>
     </row>
-    <row r="70" ht="12.0" customHeight="1">
+    <row r="70">
       <c r="A70" s="6"/>
       <c r="B70" s="6" t="s">
         <v>21</v>
@@ -3936,7 +3942,7 @@
       <c r="Y70" s="6"/>
       <c r="Z70" s="6"/>
     </row>
-    <row r="71" ht="12.0" customHeight="1">
+    <row r="71">
       <c r="A71" s="6"/>
       <c r="B71" s="7" t="s">
         <v>22</v>
@@ -3968,7 +3974,7 @@
       <c r="Y71" s="6"/>
       <c r="Z71" s="6"/>
     </row>
-    <row r="72" ht="12.0" customHeight="1">
+    <row r="72">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
         <v>24</v>
@@ -4000,7 +4006,7 @@
       <c r="Y72" s="6"/>
       <c r="Z72" s="6"/>
     </row>
-    <row r="73" ht="12.0" customHeight="1">
+    <row r="73">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -4028,7 +4034,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" ht="12.0" customHeight="1">
+    <row r="74">
       <c r="A74" s="6" t="s">
         <v>37</v>
       </c>
@@ -4058,7 +4064,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75" ht="12.0" customHeight="1">
+    <row r="75">
       <c r="A75" s="6"/>
       <c r="B75" s="6" t="s">
         <v>10</v>
@@ -4090,7 +4096,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" ht="12.0" customHeight="1">
+    <row r="76">
       <c r="A76" s="6"/>
       <c r="B76" s="6" t="s">
         <v>12</v>
@@ -4122,7 +4128,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77" ht="12.0" customHeight="1">
+    <row r="77">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
         <v>2</v>
@@ -4154,7 +4160,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78" ht="12.0" customHeight="1">
+    <row r="78">
       <c r="A78" s="6"/>
       <c r="B78" s="6" t="s">
         <v>15</v>
@@ -4186,7 +4192,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79" ht="12.0" customHeight="1">
+    <row r="79">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
         <v>16</v>
@@ -4218,7 +4224,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80" ht="12.0" customHeight="1">
+    <row r="80">
       <c r="A80" s="6"/>
       <c r="B80" s="6" t="s">
         <v>18</v>
@@ -4250,7 +4256,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81" ht="12.0" customHeight="1">
+    <row r="81">
       <c r="A81" s="6"/>
       <c r="B81" s="6" t="s">
         <v>19</v>
@@ -4282,7 +4288,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82" ht="12.0" customHeight="1">
+    <row r="82">
       <c r="A82" s="6"/>
       <c r="B82" s="6" t="s">
         <v>21</v>
@@ -4314,7 +4320,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83" ht="12.0" customHeight="1">
+    <row r="83">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>22</v>
@@ -4346,7 +4352,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84" ht="12.0" customHeight="1">
+    <row r="84">
       <c r="A84" s="6"/>
       <c r="B84" s="6" t="s">
         <v>24</v>
@@ -4378,7 +4384,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85" ht="12.0" customHeight="1">
+    <row r="85">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4406,7 +4412,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86" ht="12.0" customHeight="1">
+    <row r="86">
       <c r="A86" s="6" t="s">
         <v>41</v>
       </c>
@@ -4436,7 +4442,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87" ht="12.0" customHeight="1">
+    <row r="87">
       <c r="A87" s="6"/>
       <c r="B87" s="6" t="s">
         <v>10</v>
@@ -4468,7 +4474,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88" ht="12.0" customHeight="1">
+    <row r="88">
       <c r="A88" s="6"/>
       <c r="B88" s="6" t="s">
         <v>12</v>
@@ -4500,7 +4506,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89" ht="12.0" customHeight="1">
+    <row r="89">
       <c r="A89" s="6"/>
       <c r="B89" s="6" t="s">
         <v>2</v>
@@ -4532,7 +4538,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90" ht="12.0" customHeight="1">
+    <row r="90">
       <c r="A90" s="6"/>
       <c r="B90" s="6" t="s">
         <v>15</v>
@@ -4564,7 +4570,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91" ht="12.0" customHeight="1">
+    <row r="91">
       <c r="A91" s="6"/>
       <c r="B91" s="6" t="s">
         <v>16</v>
@@ -4596,7 +4602,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92" ht="12.0" customHeight="1">
+    <row r="92">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
         <v>18</v>
@@ -4628,7 +4634,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93" ht="12.0" customHeight="1">
+    <row r="93">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
         <v>19</v>
@@ -4660,7 +4666,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94" ht="12.0" customHeight="1">
+    <row r="94">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
         <v>21</v>
@@ -4692,7 +4698,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95" ht="12.0" customHeight="1">
+    <row r="95">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
         <v>22</v>
@@ -4724,7 +4730,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96" ht="12.0" customHeight="1">
+    <row r="96">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
         <v>24</v>
@@ -4756,7 +4762,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97" ht="12.0" customHeight="1">
+    <row r="97">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4784,7 +4790,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98" ht="12.0" customHeight="1">
+    <row r="98">
       <c r="A98" s="6" t="s">
         <v>44</v>
       </c>
@@ -4814,7 +4820,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99" ht="12.0" customHeight="1">
+    <row r="99">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
         <v>10</v>
@@ -4846,7 +4852,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100" ht="12.0" customHeight="1">
+    <row r="100">
       <c r="A100" s="6"/>
       <c r="B100" s="6" t="s">
         <v>12</v>
@@ -4878,7 +4884,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
     </row>
-    <row r="101" ht="12.0" customHeight="1">
+    <row r="101">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
         <v>2</v>
@@ -4910,7 +4916,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
-    <row r="102" ht="12.0" customHeight="1">
+    <row r="102">
       <c r="A102" s="6"/>
       <c r="B102" s="6" t="s">
         <v>15</v>
@@ -4942,7 +4948,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
     </row>
-    <row r="103" ht="12.0" customHeight="1">
+    <row r="103">
       <c r="A103" s="6"/>
       <c r="B103" s="6" t="s">
         <v>16</v>
@@ -4974,7 +4980,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
     </row>
-    <row r="104" ht="12.0" customHeight="1">
+    <row r="104">
       <c r="A104" s="6"/>
       <c r="B104" s="6" t="s">
         <v>18</v>
@@ -5006,7 +5012,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
     </row>
-    <row r="105" ht="12.0" customHeight="1">
+    <row r="105">
       <c r="A105" s="6"/>
       <c r="B105" s="6" t="s">
         <v>19</v>
@@ -5038,7 +5044,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
     </row>
-    <row r="106" ht="12.0" customHeight="1">
+    <row r="106">
       <c r="A106" s="6"/>
       <c r="B106" s="6" t="s">
         <v>21</v>
@@ -5070,7 +5076,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107" ht="12.0" customHeight="1">
+    <row r="107">
       <c r="A107" s="6"/>
       <c r="B107" s="6" t="s">
         <v>22</v>
@@ -5102,7 +5108,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108" ht="12.0" customHeight="1">
+    <row r="108">
       <c r="A108" s="6"/>
       <c r="B108" s="6" t="s">
         <v>24</v>
@@ -5134,7 +5140,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
     </row>
-    <row r="109" ht="12.0" customHeight="1">
+    <row r="109">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -5162,7 +5168,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
     </row>
-    <row r="110" ht="12.0" customHeight="1">
+    <row r="110">
       <c r="A110" s="7" t="s">
         <v>47</v>
       </c>
@@ -5192,7 +5198,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
     </row>
-    <row r="111" ht="12.0" customHeight="1">
+    <row r="111">
       <c r="A111" s="6"/>
       <c r="B111" s="6" t="s">
         <v>10</v>
@@ -5224,7 +5230,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112" ht="12.0" customHeight="1">
+    <row r="112">
       <c r="A112" s="6"/>
       <c r="B112" s="6" t="s">
         <v>12</v>
@@ -5256,7 +5262,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113" ht="12.0" customHeight="1">
+    <row r="113">
       <c r="A113" s="6"/>
       <c r="B113" s="6" t="s">
         <v>2</v>
@@ -5288,7 +5294,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114" ht="12.0" customHeight="1">
+    <row r="114">
       <c r="A114" s="6"/>
       <c r="B114" s="6" t="s">
         <v>15</v>
@@ -5318,7 +5324,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115" ht="12.0" customHeight="1">
+    <row r="115">
       <c r="A115" s="6"/>
       <c r="B115" s="6" t="s">
         <v>16</v>
@@ -5350,7 +5356,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116" ht="12.0" customHeight="1">
+    <row r="116">
       <c r="A116" s="6"/>
       <c r="B116" s="6" t="s">
         <v>50</v>
@@ -5382,7 +5388,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117" ht="12.0" customHeight="1">
+    <row r="117">
       <c r="A117" s="6"/>
       <c r="B117" s="6" t="s">
         <v>52</v>
@@ -5414,7 +5420,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118" ht="12.0" customHeight="1">
+    <row r="118">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="7"/>
@@ -5442,7 +5448,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119" ht="12.0" customHeight="1">
+    <row r="119">
       <c r="A119" s="7" t="s">
         <v>54</v>
       </c>
@@ -5472,7 +5478,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120" ht="12.0" customHeight="1">
+    <row r="120">
       <c r="A120" s="6"/>
       <c r="B120" s="6" t="s">
         <v>10</v>
@@ -5504,7 +5510,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121" ht="12.0" customHeight="1">
+    <row r="121">
       <c r="A121" s="6"/>
       <c r="B121" s="6" t="s">
         <v>12</v>
@@ -5536,7 +5542,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122" ht="12.0" customHeight="1">
+    <row r="122">
       <c r="A122" s="6"/>
       <c r="B122" s="6" t="s">
         <v>2</v>
@@ -5568,7 +5574,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123" ht="12.0" customHeight="1">
+    <row r="123">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
         <v>15</v>
@@ -5598,7 +5604,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124" ht="12.0" customHeight="1">
+    <row r="124">
       <c r="A124" s="6"/>
       <c r="B124" s="6" t="s">
         <v>16</v>
@@ -5630,7 +5636,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125" ht="12.0" customHeight="1">
+    <row r="125">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
         <v>50</v>
@@ -5662,7 +5668,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126" ht="12.0" customHeight="1">
+    <row r="126">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
         <v>52</v>
@@ -5694,7 +5700,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127" ht="12.0" customHeight="1">
+    <row r="127">
       <c r="A127" s="7"/>
       <c r="B127" s="6"/>
       <c r="C127" s="7"/>
@@ -5722,7 +5728,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128" ht="12.0" customHeight="1">
+    <row r="128">
       <c r="A128" s="7" t="s">
         <v>57</v>
       </c>
@@ -5752,7 +5758,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129" ht="12.0" customHeight="1">
+    <row r="129">
       <c r="A129" s="6"/>
       <c r="B129" s="6" t="s">
         <v>10</v>
@@ -5784,7 +5790,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130" ht="12.0" customHeight="1">
+    <row r="130">
       <c r="A130" s="6"/>
       <c r="B130" s="6" t="s">
         <v>12</v>
@@ -5816,7 +5822,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131" ht="12.0" customHeight="1">
+    <row r="131">
       <c r="A131" s="6"/>
       <c r="B131" s="6" t="s">
         <v>2</v>
@@ -5848,7 +5854,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132" ht="12.0" customHeight="1">
+    <row r="132">
       <c r="A132" s="6"/>
       <c r="B132" s="6" t="s">
         <v>15</v>
@@ -5878,7 +5884,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133" ht="12.0" customHeight="1">
+    <row r="133">
       <c r="A133" s="6"/>
       <c r="B133" s="6" t="s">
         <v>16</v>
@@ -5910,7 +5916,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134" ht="12.0" customHeight="1">
+    <row r="134">
       <c r="A134" s="6"/>
       <c r="B134" s="6" t="s">
         <v>50</v>
@@ -5942,7 +5948,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135" ht="12.0" customHeight="1">
+    <row r="135">
       <c r="A135" s="6"/>
       <c r="B135" s="6" t="s">
         <v>52</v>
@@ -5974,7 +5980,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136" ht="12.0" customHeight="1">
+    <row r="136">
       <c r="A136" s="7"/>
       <c r="B136" s="6"/>
       <c r="C136" s="7"/>
@@ -6002,7 +6008,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137" ht="12.0" customHeight="1">
+    <row r="137">
       <c r="A137" s="7" t="s">
         <v>60</v>
       </c>
@@ -6032,7 +6038,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138" ht="12.0" customHeight="1">
+    <row r="138">
       <c r="A138" s="6"/>
       <c r="B138" s="6" t="s">
         <v>10</v>
@@ -6064,7 +6070,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139" ht="12.0" customHeight="1">
+    <row r="139">
       <c r="A139" s="6"/>
       <c r="B139" s="6" t="s">
         <v>12</v>
@@ -6096,7 +6102,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140" ht="12.0" customHeight="1">
+    <row r="140">
       <c r="A140" s="6"/>
       <c r="B140" s="6" t="s">
         <v>2</v>
@@ -6128,7 +6134,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141" ht="12.0" customHeight="1">
+    <row r="141">
       <c r="A141" s="6"/>
       <c r="B141" s="6" t="s">
         <v>15</v>
@@ -6158,7 +6164,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142" ht="12.0" customHeight="1">
+    <row r="142">
       <c r="A142" s="6"/>
       <c r="B142" s="6" t="s">
         <v>16</v>
@@ -6190,7 +6196,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143" ht="12.0" customHeight="1">
+    <row r="143">
       <c r="A143" s="6"/>
       <c r="B143" s="6" t="s">
         <v>50</v>
@@ -6222,7 +6228,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144" ht="12.0" customHeight="1">
+    <row r="144">
       <c r="A144" s="6"/>
       <c r="B144" s="6" t="s">
         <v>52</v>
@@ -6254,7 +6260,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145" ht="12.0" customHeight="1">
+    <row r="145">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -6282,7 +6288,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146" ht="12.0" customHeight="1">
+    <row r="146">
       <c r="A146" s="6" t="s">
         <v>63</v>
       </c>
@@ -6312,7 +6318,7 @@
       <c r="Y146" s="6"/>
       <c r="Z146" s="6"/>
     </row>
-    <row r="147" ht="12.0" customHeight="1">
+    <row r="147">
       <c r="A147" s="6"/>
       <c r="B147" s="6" t="s">
         <v>10</v>
@@ -6344,7 +6350,7 @@
       <c r="Y147" s="6"/>
       <c r="Z147" s="6"/>
     </row>
-    <row r="148" ht="12.0" customHeight="1">
+    <row r="148">
       <c r="A148" s="6"/>
       <c r="B148" s="6" t="s">
         <v>12</v>
@@ -6376,7 +6382,7 @@
       <c r="Y148" s="6"/>
       <c r="Z148" s="6"/>
     </row>
-    <row r="149" ht="12.0" customHeight="1">
+    <row r="149">
       <c r="A149" s="6"/>
       <c r="B149" s="6" t="s">
         <v>2</v>
@@ -6408,7 +6414,7 @@
       <c r="Y149" s="6"/>
       <c r="Z149" s="6"/>
     </row>
-    <row r="150" ht="12.0" customHeight="1">
+    <row r="150">
       <c r="A150" s="6"/>
       <c r="B150" s="6" t="s">
         <v>15</v>
@@ -6438,7 +6444,7 @@
       <c r="Y150" s="6"/>
       <c r="Z150" s="6"/>
     </row>
-    <row r="151" ht="12.0" customHeight="1">
+    <row r="151">
       <c r="A151" s="6"/>
       <c r="B151" s="6" t="s">
         <v>16</v>
@@ -6470,7 +6476,7 @@
       <c r="Y151" s="6"/>
       <c r="Z151" s="6"/>
     </row>
-    <row r="152" ht="12.0" customHeight="1">
+    <row r="152">
       <c r="A152" s="6"/>
       <c r="B152" s="6" t="s">
         <v>50</v>
@@ -6502,7 +6508,7 @@
       <c r="Y152" s="6"/>
       <c r="Z152" s="6"/>
     </row>
-    <row r="153" ht="12.0" customHeight="1">
+    <row r="153">
       <c r="A153" s="6"/>
       <c r="B153" s="6" t="s">
         <v>52</v>
@@ -6534,7 +6540,7 @@
       <c r="Y153" s="6"/>
       <c r="Z153" s="6"/>
     </row>
-    <row r="154" ht="12.0" customHeight="1">
+    <row r="154">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -6562,7 +6568,7 @@
       <c r="Y154" s="6"/>
       <c r="Z154" s="6"/>
     </row>
-    <row r="155" ht="12.0" customHeight="1">
+    <row r="155">
       <c r="A155" s="6" t="s">
         <v>66</v>
       </c>
@@ -6592,7 +6598,7 @@
       <c r="Y155" s="6"/>
       <c r="Z155" s="6"/>
     </row>
-    <row r="156" ht="12.0" customHeight="1">
+    <row r="156">
       <c r="A156" s="6"/>
       <c r="B156" s="6" t="s">
         <v>10</v>
@@ -6624,7 +6630,7 @@
       <c r="Y156" s="6"/>
       <c r="Z156" s="6"/>
     </row>
-    <row r="157" ht="12.0" customHeight="1">
+    <row r="157">
       <c r="A157" s="6"/>
       <c r="B157" s="6" t="s">
         <v>12</v>
@@ -6656,7 +6662,7 @@
       <c r="Y157" s="6"/>
       <c r="Z157" s="6"/>
     </row>
-    <row r="158" ht="12.0" customHeight="1">
+    <row r="158">
       <c r="A158" s="6"/>
       <c r="B158" s="6" t="s">
         <v>2</v>
@@ -6688,7 +6694,7 @@
       <c r="Y158" s="6"/>
       <c r="Z158" s="6"/>
     </row>
-    <row r="159" ht="12.0" customHeight="1">
+    <row r="159">
       <c r="A159" s="6"/>
       <c r="B159" s="6" t="s">
         <v>15</v>
@@ -6718,7 +6724,7 @@
       <c r="Y159" s="6"/>
       <c r="Z159" s="6"/>
     </row>
-    <row r="160" ht="12.0" customHeight="1">
+    <row r="160">
       <c r="A160" s="6"/>
       <c r="B160" s="6" t="s">
         <v>16</v>
@@ -6750,7 +6756,7 @@
       <c r="Y160" s="6"/>
       <c r="Z160" s="6"/>
     </row>
-    <row r="161" ht="12.0" customHeight="1">
+    <row r="161">
       <c r="A161" s="6"/>
       <c r="B161" s="6" t="s">
         <v>50</v>
@@ -6782,7 +6788,7 @@
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
     </row>
-    <row r="162" ht="12.0" customHeight="1">
+    <row r="162">
       <c r="A162" s="6"/>
       <c r="B162" s="6" t="s">
         <v>52</v>
@@ -6814,7 +6820,7 @@
       <c r="Y162" s="6"/>
       <c r="Z162" s="6"/>
     </row>
-    <row r="163" ht="12.0" customHeight="1">
+    <row r="163">
       <c r="A163" s="13"/>
       <c r="B163" s="13"/>
       <c r="C163" s="13"/>
@@ -6842,7 +6848,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164" ht="12.0" customHeight="1">
+    <row r="164">
       <c r="A164" s="10" t="s">
         <v>69</v>
       </c>
@@ -6872,7 +6878,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165" ht="12.0" customHeight="1">
+    <row r="165">
       <c r="A165" s="6"/>
       <c r="B165" s="6" t="s">
         <v>10</v>
@@ -6904,7 +6910,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
     </row>
-    <row r="166" ht="12.0" customHeight="1">
+    <row r="166">
       <c r="A166" s="6"/>
       <c r="B166" s="6" t="s">
         <v>12</v>
@@ -6936,7 +6942,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
     </row>
-    <row r="167" ht="12.0" customHeight="1">
+    <row r="167">
       <c r="A167" s="6"/>
       <c r="B167" s="6" t="s">
         <v>2</v>
@@ -6968,7 +6974,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168">
       <c r="A168" s="6"/>
       <c r="B168" s="6" t="s">
         <v>15</v>
@@ -6998,7 +7004,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169">
       <c r="A169" s="6"/>
       <c r="B169" s="6" t="s">
         <v>16</v>
@@ -7030,7 +7036,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170">
       <c r="A170" s="6"/>
       <c r="B170" s="6" t="s">
         <v>50</v>
@@ -7062,7 +7068,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171">
       <c r="A171" s="6"/>
       <c r="B171" s="6" t="s">
         <v>52</v>
@@ -7094,7 +7100,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -7122,7 +7128,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173">
       <c r="A173" s="10" t="s">
         <v>73</v>
       </c>
@@ -7152,7 +7158,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174">
       <c r="A174" s="6"/>
       <c r="B174" s="6" t="s">
         <v>10</v>
@@ -7184,7 +7190,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175">
       <c r="A175" s="6"/>
       <c r="B175" s="6" t="s">
         <v>12</v>
@@ -7216,7 +7222,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176">
       <c r="A176" s="6"/>
       <c r="B176" s="6" t="s">
         <v>2</v>
@@ -7248,7 +7254,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177">
       <c r="A177" s="6"/>
       <c r="B177" s="6" t="s">
         <v>15</v>
@@ -7278,7 +7284,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178">
       <c r="A178" s="6"/>
       <c r="B178" s="6" t="s">
         <v>16</v>
@@ -7310,7 +7316,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179">
       <c r="A179" s="6"/>
       <c r="B179" s="6" t="s">
         <v>50</v>
@@ -7342,7 +7348,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180">
       <c r="A180" s="6"/>
       <c r="B180" s="6" t="s">
         <v>52</v>
@@ -7374,7 +7380,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -7402,7 +7408,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182">
       <c r="A182" s="6" t="s">
         <v>77</v>
       </c>
@@ -7432,7 +7438,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183">
       <c r="A183" s="6"/>
       <c r="B183" s="6" t="s">
         <v>10</v>
@@ -7464,7 +7470,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184">
       <c r="A184" s="6"/>
       <c r="B184" s="6" t="s">
         <v>12</v>
@@ -7496,7 +7502,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185">
       <c r="A185" s="6"/>
       <c r="B185" s="6" t="s">
         <v>2</v>
@@ -7528,7 +7534,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186">
       <c r="A186" s="6"/>
       <c r="B186" s="6" t="s">
         <v>15</v>
@@ -7558,7 +7564,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187">
       <c r="A187" s="6"/>
       <c r="B187" s="6" t="s">
         <v>16</v>
@@ -7590,7 +7596,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188">
       <c r="A188" s="6"/>
       <c r="B188" s="6" t="s">
         <v>50</v>
@@ -7622,7 +7628,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189">
       <c r="A189" s="6"/>
       <c r="B189" s="6" t="s">
         <v>52</v>

--- a/product-definitions/spreadsheet/pm-concentration.xlsx
+++ b/product-definitions/spreadsheet/pm-concentration.xlsx
@@ -2366,7 +2366,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6" t="s">
         <v>19</v>
@@ -2398,7 +2398,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
         <v>21</v>
@@ -2430,7 +2430,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="7" t="s">
         <v>22</v>
@@ -2462,7 +2462,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
         <v>24</v>
@@ -2494,7 +2494,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
@@ -2522,7 +2522,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -2552,7 +2552,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6" t="s">
         <v>12</v>
@@ -2616,7 +2616,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
         <v>2</v>
@@ -2648,7 +2648,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
         <v>15</v>
@@ -2680,7 +2680,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
         <v>16</v>
@@ -2712,7 +2712,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
         <v>18</v>
@@ -2744,7 +2744,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6" t="s">
         <v>19</v>
@@ -2776,7 +2776,7 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6" t="s">
         <v>21</v>
@@ -2808,7 +2808,7 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="7" t="s">
         <v>22</v>
@@ -2840,7 +2840,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="6" t="s">
         <v>24</v>
@@ -2872,7 +2872,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
@@ -2900,7 +2900,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="s">
         <v>30</v>
       </c>
@@ -2930,7 +2930,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6" t="s">
         <v>12</v>
@@ -2994,7 +2994,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="6" t="s">
         <v>2</v>
@@ -3026,7 +3026,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="6" t="s">
         <v>15</v>
@@ -3058,7 +3058,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="6" t="s">
         <v>16</v>
@@ -3090,7 +3090,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
         <v>18</v>
@@ -3122,7 +3122,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
         <v>19</v>
@@ -3154,7 +3154,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6"/>
       <c r="B46" s="6" t="s">
         <v>21</v>
@@ -3186,7 +3186,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="7" t="s">
         <v>22</v>
@@ -3218,7 +3218,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
         <v>24</v>
@@ -3250,7 +3250,7 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3278,7 +3278,7 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="s">
         <v>32</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="Y50" s="6"/>
       <c r="Z50" s="6"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
         <v>10</v>
@@ -3340,7 +3340,7 @@
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="6" t="s">
         <v>12</v>
@@ -3372,7 +3372,7 @@
       <c r="Y52" s="6"/>
       <c r="Z52" s="6"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
         <v>2</v>
@@ -3404,7 +3404,7 @@
       <c r="Y53" s="6"/>
       <c r="Z53" s="6"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="6" t="s">
         <v>15</v>
@@ -3436,7 +3436,7 @@
       <c r="Y54" s="6"/>
       <c r="Z54" s="6"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="6"/>
       <c r="B55" s="6" t="s">
         <v>16</v>
@@ -3468,7 +3468,7 @@
       <c r="Y55" s="6"/>
       <c r="Z55" s="6"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6"/>
       <c r="B56" s="6" t="s">
         <v>18</v>
@@ -3500,7 +3500,7 @@
       <c r="Y56" s="6"/>
       <c r="Z56" s="6"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="6" t="s">
         <v>19</v>
@@ -3532,7 +3532,7 @@
       <c r="Y57" s="6"/>
       <c r="Z57" s="6"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>21</v>
@@ -3564,7 +3564,7 @@
       <c r="Y58" s="6"/>
       <c r="Z58" s="6"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="7" t="s">
         <v>22</v>
@@ -3596,7 +3596,7 @@
       <c r="Y59" s="6"/>
       <c r="Z59" s="6"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
         <v>24</v>
@@ -3628,7 +3628,7 @@
       <c r="Y60" s="6"/>
       <c r="Z60" s="6"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -3656,7 +3656,7 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="10" t="s">
         <v>34</v>
       </c>
@@ -3686,7 +3686,7 @@
       <c r="Y62" s="6"/>
       <c r="Z62" s="6"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
         <v>10</v>
@@ -3718,7 +3718,7 @@
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
         <v>12</v>
@@ -3750,7 +3750,7 @@
       <c r="Y64" s="6"/>
       <c r="Z64" s="6"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="6" t="s">
         <v>2</v>
@@ -3782,7 +3782,7 @@
       <c r="Y65" s="6"/>
       <c r="Z65" s="6"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="6" t="s">
         <v>15</v>
@@ -3814,7 +3814,7 @@
       <c r="Y66" s="6"/>
       <c r="Z66" s="6"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6" t="s">
         <v>16</v>
@@ -3846,7 +3846,7 @@
       <c r="Y67" s="6"/>
       <c r="Z67" s="6"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
         <v>18</v>
@@ -3878,7 +3878,7 @@
       <c r="Y68" s="6"/>
       <c r="Z68" s="6"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="6" t="s">
         <v>19</v>
@@ -3910,7 +3910,7 @@
       <c r="Y69" s="6"/>
       <c r="Z69" s="6"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6"/>
       <c r="B70" s="6" t="s">
         <v>21</v>
@@ -3942,7 +3942,7 @@
       <c r="Y70" s="6"/>
       <c r="Z70" s="6"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="7" t="s">
         <v>22</v>
@@ -3974,7 +3974,7 @@
       <c r="Y71" s="6"/>
       <c r="Z71" s="6"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
         <v>24</v>
@@ -4006,7 +4006,7 @@
       <c r="Y72" s="6"/>
       <c r="Z72" s="6"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -4034,7 +4034,7 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
         <v>37</v>
       </c>
@@ -4064,7 +4064,7 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="6" t="s">
         <v>10</v>
@@ -4096,7 +4096,7 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="6" t="s">
         <v>12</v>
@@ -4128,7 +4128,7 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
         <v>2</v>
@@ -4160,7 +4160,7 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6"/>
       <c r="B78" s="6" t="s">
         <v>15</v>
@@ -4192,7 +4192,7 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6" t="s">
         <v>16</v>
@@ -4224,7 +4224,7 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6"/>
       <c r="B80" s="6" t="s">
         <v>18</v>
@@ -4256,7 +4256,7 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="6"/>
       <c r="B81" s="6" t="s">
         <v>19</v>
@@ -4288,7 +4288,7 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="6" t="s">
         <v>21</v>
@@ -4320,7 +4320,7 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>22</v>
@@ -4352,7 +4352,7 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6"/>
       <c r="B84" s="6" t="s">
         <v>24</v>
@@ -4384,7 +4384,7 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4412,7 +4412,7 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
         <v>41</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="6" t="s">
         <v>10</v>
@@ -4474,7 +4474,7 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="6" t="s">
         <v>12</v>
@@ -4506,7 +4506,7 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="6" t="s">
         <v>2</v>
@@ -4538,7 +4538,7 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="6" t="s">
         <v>15</v>
@@ -4570,7 +4570,7 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6"/>
       <c r="B91" s="6" t="s">
         <v>16</v>
@@ -4602,7 +4602,7 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="6"/>
       <c r="B92" s="6" t="s">
         <v>18</v>
@@ -4634,7 +4634,7 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="6" t="s">
         <v>19</v>
@@ -4666,7 +4666,7 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="6" t="s">
         <v>21</v>
@@ -4698,7 +4698,7 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="6" t="s">
         <v>22</v>
@@ -4730,7 +4730,7 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="6" t="s">
         <v>24</v>
@@ -4762,7 +4762,7 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4790,7 +4790,7 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>44</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="6" t="s">
         <v>10</v>
@@ -4852,7 +4852,7 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="6"/>
       <c r="B100" s="6" t="s">
         <v>12</v>
@@ -4884,7 +4884,7 @@
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6"/>
       <c r="B101" s="6" t="s">
         <v>2</v>
@@ -4916,7 +4916,7 @@
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="6" t="s">
         <v>15</v>
@@ -4948,7 +4948,7 @@
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6"/>
       <c r="B103" s="6" t="s">
         <v>16</v>
@@ -4980,7 +4980,7 @@
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="6" t="s">
         <v>18</v>
@@ -5012,7 +5012,7 @@
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="6" t="s">
         <v>19</v>
@@ -5044,7 +5044,7 @@
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="6" t="s">
         <v>21</v>
@@ -5076,7 +5076,7 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6"/>
       <c r="B107" s="6" t="s">
         <v>22</v>
@@ -5108,7 +5108,7 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="6"/>
       <c r="B108" s="6" t="s">
         <v>24</v>
@@ -5140,7 +5140,7 @@
       <c r="Y108" s="5"/>
       <c r="Z108" s="5"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -5168,7 +5168,7 @@
       <c r="Y109" s="5"/>
       <c r="Z109" s="5"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="7" t="s">
         <v>47</v>
       </c>
@@ -5198,7 +5198,7 @@
       <c r="Y110" s="5"/>
       <c r="Z110" s="5"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6"/>
       <c r="B111" s="6" t="s">
         <v>10</v>
@@ -5230,7 +5230,7 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="6"/>
       <c r="B112" s="6" t="s">
         <v>12</v>
@@ -5262,7 +5262,7 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6"/>
       <c r="B113" s="6" t="s">
         <v>2</v>
@@ -5294,7 +5294,7 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6"/>
       <c r="B114" s="6" t="s">
         <v>15</v>
@@ -5324,7 +5324,7 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6"/>
       <c r="B115" s="6" t="s">
         <v>16</v>
@@ -5356,7 +5356,7 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6"/>
       <c r="B116" s="6" t="s">
         <v>50</v>
@@ -5388,7 +5388,7 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6"/>
       <c r="B117" s="6" t="s">
         <v>52</v>
@@ -5420,7 +5420,7 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="7"/>
@@ -5448,7 +5448,7 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="7" t="s">
         <v>54</v>
       </c>
@@ -5478,7 +5478,7 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="6" t="s">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6"/>
       <c r="B121" s="6" t="s">
         <v>12</v>
@@ -5542,7 +5542,7 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6"/>
       <c r="B122" s="6" t="s">
         <v>2</v>
@@ -5574,7 +5574,7 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
         <v>15</v>
@@ -5604,7 +5604,7 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6"/>
       <c r="B124" s="6" t="s">
         <v>16</v>
@@ -5636,7 +5636,7 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
         <v>50</v>
@@ -5668,7 +5668,7 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
         <v>52</v>
@@ -5700,7 +5700,7 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="7"/>
       <c r="B127" s="6"/>
       <c r="C127" s="7"/>
@@ -5728,7 +5728,7 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="7" t="s">
         <v>57</v>
       </c>
@@ -5758,7 +5758,7 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6"/>
       <c r="B129" s="6" t="s">
         <v>10</v>
@@ -5790,7 +5790,7 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6"/>
       <c r="B130" s="6" t="s">
         <v>12</v>
@@ -5822,7 +5822,7 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6"/>
       <c r="B131" s="6" t="s">
         <v>2</v>
@@ -5854,7 +5854,7 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6"/>
       <c r="B132" s="6" t="s">
         <v>15</v>
@@ -5884,7 +5884,7 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6"/>
       <c r="B133" s="6" t="s">
         <v>16</v>
@@ -5916,7 +5916,7 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6"/>
       <c r="B134" s="6" t="s">
         <v>50</v>
@@ -5948,7 +5948,7 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6"/>
       <c r="B135" s="6" t="s">
         <v>52</v>
@@ -5980,7 +5980,7 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="6"/>
       <c r="C136" s="7"/>
@@ -6008,7 +6008,7 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="7" t="s">
         <v>60</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6"/>
       <c r="B138" s="6" t="s">
         <v>10</v>
@@ -6070,7 +6070,7 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="6"/>
       <c r="B139" s="6" t="s">
         <v>12</v>
@@ -6102,7 +6102,7 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6"/>
       <c r="B140" s="6" t="s">
         <v>2</v>
@@ -6134,7 +6134,7 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6"/>
       <c r="B141" s="6" t="s">
         <v>15</v>
@@ -6164,7 +6164,7 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6"/>
       <c r="B142" s="6" t="s">
         <v>16</v>
@@ -6196,7 +6196,7 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6"/>
       <c r="B143" s="6" t="s">
         <v>50</v>
@@ -6228,7 +6228,7 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6"/>
       <c r="B144" s="6" t="s">
         <v>52</v>
@@ -6260,7 +6260,7 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -6288,7 +6288,7 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
         <v>63</v>
       </c>
@@ -6318,7 +6318,7 @@
       <c r="Y146" s="6"/>
       <c r="Z146" s="6"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="6"/>
       <c r="B147" s="6" t="s">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       <c r="Y147" s="6"/>
       <c r="Z147" s="6"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="6"/>
       <c r="B148" s="6" t="s">
         <v>12</v>
@@ -6382,7 +6382,7 @@
       <c r="Y148" s="6"/>
       <c r="Z148" s="6"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="6"/>
       <c r="B149" s="6" t="s">
         <v>2</v>
@@ -6414,7 +6414,7 @@
       <c r="Y149" s="6"/>
       <c r="Z149" s="6"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="6" t="s">
         <v>15</v>
@@ -6444,7 +6444,7 @@
       <c r="Y150" s="6"/>
       <c r="Z150" s="6"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="6"/>
       <c r="B151" s="6" t="s">
         <v>16</v>
@@ -6476,7 +6476,7 @@
       <c r="Y151" s="6"/>
       <c r="Z151" s="6"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="6"/>
       <c r="B152" s="6" t="s">
         <v>50</v>
@@ -6508,7 +6508,7 @@
       <c r="Y152" s="6"/>
       <c r="Z152" s="6"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="6"/>
       <c r="B153" s="6" t="s">
         <v>52</v>
@@ -6540,7 +6540,7 @@
       <c r="Y153" s="6"/>
       <c r="Z153" s="6"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -6568,7 +6568,7 @@
       <c r="Y154" s="6"/>
       <c r="Z154" s="6"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
         <v>66</v>
       </c>
@@ -6598,7 +6598,7 @@
       <c r="Y155" s="6"/>
       <c r="Z155" s="6"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="6"/>
       <c r="B156" s="6" t="s">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       <c r="Y156" s="6"/>
       <c r="Z156" s="6"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="6"/>
       <c r="B157" s="6" t="s">
         <v>12</v>
@@ -6662,7 +6662,7 @@
       <c r="Y157" s="6"/>
       <c r="Z157" s="6"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="6"/>
       <c r="B158" s="6" t="s">
         <v>2</v>
@@ -6694,7 +6694,7 @@
       <c r="Y158" s="6"/>
       <c r="Z158" s="6"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="6"/>
       <c r="B159" s="6" t="s">
         <v>15</v>
@@ -6724,7 +6724,7 @@
       <c r="Y159" s="6"/>
       <c r="Z159" s="6"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="6"/>
       <c r="B160" s="6" t="s">
         <v>16</v>
@@ -6756,7 +6756,7 @@
       <c r="Y160" s="6"/>
       <c r="Z160" s="6"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6"/>
       <c r="B161" s="6" t="s">
         <v>50</v>
@@ -6788,7 +6788,7 @@
       <c r="Y161" s="6"/>
       <c r="Z161" s="6"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="6"/>
       <c r="B162" s="6" t="s">
         <v>52</v>
@@ -6820,7 +6820,7 @@
       <c r="Y162" s="6"/>
       <c r="Z162" s="6"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="13"/>
       <c r="B163" s="13"/>
       <c r="C163" s="13"/>
@@ -6848,7 +6848,7 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="10" t="s">
         <v>69</v>
       </c>
@@ -6878,7 +6878,7 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="6"/>
       <c r="B165" s="6" t="s">
         <v>10</v>
@@ -6910,7 +6910,7 @@
       <c r="Y165" s="5"/>
       <c r="Z165" s="5"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="6"/>
       <c r="B166" s="6" t="s">
         <v>12</v>
@@ -6942,7 +6942,7 @@
       <c r="Y166" s="5"/>
       <c r="Z166" s="5"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="6"/>
       <c r="B167" s="6" t="s">
         <v>2</v>
@@ -6974,7 +6974,7 @@
       <c r="Y167" s="5"/>
       <c r="Z167" s="5"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="6" t="s">
         <v>15</v>
@@ -7004,7 +7004,7 @@
       <c r="Y168" s="5"/>
       <c r="Z168" s="5"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="6"/>
       <c r="B169" s="6" t="s">
         <v>16</v>
@@ -7036,7 +7036,7 @@
       <c r="Y169" s="5"/>
       <c r="Z169" s="5"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6"/>
       <c r="B170" s="6" t="s">
         <v>50</v>
@@ -7068,7 +7068,7 @@
       <c r="Y170" s="5"/>
       <c r="Z170" s="5"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="6"/>
       <c r="B171" s="6" t="s">
         <v>52</v>
@@ -7100,7 +7100,7 @@
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -7128,7 +7128,7 @@
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="10" t="s">
         <v>73</v>
       </c>
@@ -7158,7 +7158,7 @@
       <c r="Y173" s="5"/>
       <c r="Z173" s="5"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="6"/>
       <c r="B174" s="6" t="s">
         <v>10</v>
@@ -7190,7 +7190,7 @@
       <c r="Y174" s="5"/>
       <c r="Z174" s="5"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="6"/>
       <c r="B175" s="6" t="s">
         <v>12</v>
@@ -7222,7 +7222,7 @@
       <c r="Y175" s="5"/>
       <c r="Z175" s="5"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="6"/>
       <c r="B176" s="6" t="s">
         <v>2</v>
@@ -7254,7 +7254,7 @@
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="6"/>
       <c r="B177" s="6" t="s">
         <v>15</v>
@@ -7284,7 +7284,7 @@
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="6"/>
       <c r="B178" s="6" t="s">
         <v>16</v>
@@ -7316,7 +7316,7 @@
       <c r="Y178" s="5"/>
       <c r="Z178" s="5"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="6"/>
       <c r="B179" s="6" t="s">
         <v>50</v>
@@ -7348,7 +7348,7 @@
       <c r="Y179" s="5"/>
       <c r="Z179" s="5"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="6"/>
       <c r="B180" s="6" t="s">
         <v>52</v>
@@ -7380,7 +7380,7 @@
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -7408,7 +7408,7 @@
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="6" t="s">
         <v>77</v>
       </c>
@@ -7438,7 +7438,7 @@
       <c r="Y182" s="5"/>
       <c r="Z182" s="5"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="6"/>
       <c r="B183" s="6" t="s">
         <v>10</v>
@@ -7470,7 +7470,7 @@
       <c r="Y183" s="5"/>
       <c r="Z183" s="5"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="6"/>
       <c r="B184" s="6" t="s">
         <v>12</v>
@@ -7502,7 +7502,7 @@
       <c r="Y184" s="5"/>
       <c r="Z184" s="5"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="6"/>
       <c r="B185" s="6" t="s">
         <v>2</v>
@@ -7534,7 +7534,7 @@
       <c r="Y185" s="5"/>
       <c r="Z185" s="5"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="6"/>
       <c r="B186" s="6" t="s">
         <v>15</v>
@@ -7564,7 +7564,7 @@
       <c r="Y186" s="5"/>
       <c r="Z186" s="5"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="6"/>
       <c r="B187" s="6" t="s">
         <v>16</v>
@@ -7596,7 +7596,7 @@
       <c r="Y187" s="5"/>
       <c r="Z187" s="5"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="6"/>
       <c r="B188" s="6" t="s">
         <v>50</v>
@@ -7628,7 +7628,7 @@
       <c r="Y188" s="5"/>
       <c r="Z188" s="5"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="6"/>
       <c r="B189" s="6" t="s">
         <v>52</v>
